--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/40_CYBERSECURITY/valcanary_stig_checklist_rollup_2024.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/40_CYBERSECURITY/valcanary_stig_checklist_rollup_2024.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
